--- a/pds_admin_WB/Backend/Backend/Tagging_Sheet_Pre_leg1.xlsx
+++ b/pds_admin_WB/Backend/Backend/Tagging_Sheet_Pre_leg1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Var</t>
   </si>
@@ -40,34 +40,16 @@
     <t>X</t>
   </si>
   <si>
-    <t>EBDNFM1</t>
-  </si>
-  <si>
-    <t>EF14003</t>
-  </si>
-  <si>
     <t>Kolkata</t>
   </si>
   <si>
-    <t>PurbaBardhaman</t>
-  </si>
-  <si>
-    <t>PaschimBardhaman</t>
-  </si>
-  <si>
-    <t>Wheat</t>
-  </si>
-  <si>
-    <t>Atta</t>
-  </si>
-  <si>
-    <t>391.48825</t>
-  </si>
-  <si>
-    <t>748.64</t>
-  </si>
-  <si>
-    <t>46.26</t>
+    <t>Alipurduar</t>
+  </si>
+  <si>
+    <t>WheatR</t>
+  </si>
+  <si>
+    <t>16.0</t>
   </si>
 </sst>
 </file>
@@ -425,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -462,123 +444,19 @@
         <v>611</v>
       </c>
       <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="E2">
-        <v>611</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
         <v>11</v>
-      </c>
-      <c r="E3">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
